--- a/项目管理工具/tests/fixtures/RW2026-001-隔离网关【20260617】.xlsx
+++ b/项目管理工具/tests/fixtures/RW2026-001-隔离网关【20260617】.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="18350" windowHeight="8080"/>
+    <workbookView windowWidth="23840" windowHeight="12220"/>
   </bookViews>
   <sheets>
     <sheet name="业务填写表" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="167" uniqueCount="119">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="120">
   <si>
     <t>业务填写表</t>
   </si>
@@ -118,6 +118,9 @@
       </rPr>
       <t>★</t>
     </r>
+  </si>
+  <si>
+    <t>RW2026-001</t>
   </si>
   <si>
     <r>
@@ -1987,6 +1990,13 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="14"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Arial"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <i/>
       <sz val="16"/>
       <color rgb="FF888888"/>
@@ -1994,13 +2004,6 @@
       <charset val="134"/>
     </font>
     <font>
-      <b/>
-      <sz val="14"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Arial"/>
-      <charset val="134"/>
-    </font>
-    <font>
       <i/>
       <sz val="12"/>
       <color rgb="FFFF0000"/>
@@ -2017,15 +2020,15 @@
     <font>
       <i/>
       <sz val="14"/>
+      <color rgb="FFBDD7EE"/>
+      <name val="Arial"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="14"/>
       <color rgb="FF555555"/>
       <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="14"/>
-      <color rgb="FFBDD7EE"/>
-      <name val="Arial"/>
       <charset val="134"/>
     </font>
   </fonts>
@@ -3198,19 +3201,19 @@
     <tabColor rgb="FF70AD47"/>
   </sheetPr>
   <dimension ref="A1:K64"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
     <col min="2" max="2" width="13" customWidth="1"/>
-    <col min="3" max="3" width="26.4454545454545" customWidth="1"/>
-    <col min="4" max="4" width="22.2727272727273" customWidth="1"/>
-    <col min="5" max="5" width="28.7272727272727" customWidth="1"/>
-    <col min="6" max="6" width="15.4545454545455" customWidth="1"/>
-    <col min="7" max="7" width="23.6363636363636" customWidth="1"/>
-    <col min="8" max="8" width="16.1" style="2" customWidth="1"/>
-    <col min="9" max="9" width="16.1" customWidth="1"/>
+    <col min="3" max="3" width="26.4423076923077" customWidth="1"/>
+    <col min="4" max="4" width="22.2692307692308" customWidth="1"/>
+    <col min="5" max="5" width="28.7307692307692" customWidth="1"/>
+    <col min="6" max="6" width="15.4519230769231" customWidth="1"/>
+    <col min="7" max="7" width="23.6346153846154" customWidth="1"/>
+    <col min="8" max="8" width="16.0961538461538" style="2" customWidth="1"/>
+    <col min="9" max="9" width="16.0961538461538" customWidth="1"/>
     <col min="10" max="10" width="12" customWidth="1"/>
-    <col min="11" max="11" width="34.9" customWidth="1"/>
+    <col min="11" max="11" width="34.9038461538462" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="44" customHeight="1" spans="1:11">
@@ -3230,7 +3233,7 @@
       <c r="J1" s="7"/>
       <c r="K1" s="8"/>
     </row>
-    <row r="2" customHeight="1" spans="1:11">
+    <row r="2" ht="14" customHeight="1" spans="1:11">
       <c r="A2" s="9"/>
       <c r="B2" s="9"/>
       <c r="C2" s="9"/>
@@ -3262,22 +3265,22 @@
       <c r="A4" s="15" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="16">
-        <v>125</v>
+      <c r="B4" s="16" t="s">
+        <v>4</v>
       </c>
       <c r="C4" s="17"/>
       <c r="D4" s="15" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E4" s="18" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F4" s="17"/>
       <c r="G4" s="15" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H4" s="19" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I4" s="20"/>
       <c r="J4" s="20"/>
@@ -3285,10 +3288,10 @@
     </row>
     <row r="5" ht="26" customHeight="1" spans="1:11">
       <c r="A5" s="15" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B5" s="18" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C5" s="20"/>
       <c r="D5" s="20"/>
@@ -3302,24 +3305,24 @@
     </row>
     <row r="6" ht="40" customHeight="1" spans="1:11">
       <c r="A6" s="15" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B6" s="18" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C6" s="17"/>
       <c r="D6" s="15" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E6" s="18" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F6" s="17"/>
       <c r="G6" s="15" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H6" s="19" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I6" s="20"/>
       <c r="J6" s="20"/>
@@ -3327,10 +3330,10 @@
     </row>
     <row r="7" ht="32" customHeight="1" spans="1:11">
       <c r="A7" s="15" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B7" s="18" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C7" s="20"/>
       <c r="D7" s="20"/>
@@ -3344,10 +3347,10 @@
     </row>
     <row r="8" ht="32" customHeight="1" spans="1:11">
       <c r="A8" s="15" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B8" s="18" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C8" s="20"/>
       <c r="D8" s="20"/>
@@ -3361,21 +3364,21 @@
     </row>
     <row r="9" ht="26" customHeight="1" spans="1:11">
       <c r="A9" s="15" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B9" s="22">
         <v>46128</v>
       </c>
       <c r="C9" s="17"/>
       <c r="D9" s="15" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E9" s="22">
         <v>46188</v>
       </c>
       <c r="F9" s="17"/>
       <c r="G9" s="15" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H9" s="23"/>
       <c r="I9" s="20"/>
@@ -3384,17 +3387,17 @@
     </row>
     <row r="10" ht="26" customHeight="1" spans="1:11">
       <c r="A10" s="15" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B10" s="24">
         <v>65</v>
       </c>
       <c r="C10" s="17"/>
       <c r="D10" s="15" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E10" s="18" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F10" s="20"/>
       <c r="G10" s="20"/>
@@ -3405,10 +3408,10 @@
     </row>
     <row r="11" ht="32" customHeight="1" spans="1:11">
       <c r="A11" s="15" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B11" s="18" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C11" s="20"/>
       <c r="D11" s="20"/>
@@ -3422,7 +3425,7 @@
     </row>
     <row r="12" ht="32" customHeight="1" spans="1:11">
       <c r="A12" s="15" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B12" s="18"/>
       <c r="C12" s="20"/>
@@ -3450,7 +3453,7 @@
     </row>
     <row r="14" ht="33" customHeight="1" spans="1:11">
       <c r="A14" s="25" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B14" s="26"/>
       <c r="C14" s="26"/>
@@ -3465,17 +3468,17 @@
     </row>
     <row r="15" ht="26" customHeight="1" spans="1:11">
       <c r="A15" s="15" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B15" s="29"/>
       <c r="C15" s="30"/>
       <c r="D15" s="15" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E15" s="31"/>
       <c r="F15" s="30"/>
       <c r="G15" s="15" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H15" s="32"/>
       <c r="I15" s="33"/>
@@ -3484,17 +3487,17 @@
     </row>
     <row r="16" ht="26" customHeight="1" spans="1:11">
       <c r="A16" s="15" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B16" s="34"/>
       <c r="C16" s="30"/>
       <c r="D16" s="15" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E16" s="34"/>
       <c r="F16" s="30"/>
       <c r="G16" s="15" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H16" s="35"/>
       <c r="I16" s="33"/>
@@ -3503,17 +3506,17 @@
     </row>
     <row r="17" ht="26" customHeight="1" spans="1:11">
       <c r="A17" s="15" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B17" s="18" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C17" s="17"/>
       <c r="D17" s="15" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E17" s="18" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F17" s="20"/>
       <c r="G17" s="20"/>
@@ -3524,7 +3527,7 @@
     </row>
     <row r="18" ht="26" customHeight="1" spans="1:11">
       <c r="A18" s="15" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B18" s="29"/>
       <c r="C18" s="33"/>
@@ -3539,21 +3542,21 @@
     </row>
     <row r="19" ht="26" customHeight="1" spans="1:11">
       <c r="A19" s="15" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B19" s="22">
         <v>46190</v>
       </c>
       <c r="C19" s="17"/>
       <c r="D19" s="15" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E19" s="18" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F19" s="17"/>
       <c r="G19" s="37" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="H19" s="38"/>
       <c r="I19" s="1"/>
@@ -3575,7 +3578,7 @@
     </row>
     <row r="21" ht="24" customHeight="1" spans="1:11">
       <c r="A21" s="11" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B21" s="12"/>
       <c r="C21" s="12"/>
@@ -3590,7 +3593,7 @@
     </row>
     <row r="22" ht="38" customHeight="1" spans="1:11">
       <c r="A22" s="39" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B22" s="1"/>
       <c r="C22" s="1"/>
@@ -3605,47 +3608,47 @@
     </row>
     <row r="23" s="1" customFormat="1" ht="26" customHeight="1" spans="1:11">
       <c r="A23" s="40" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B23" s="40" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C23" s="40" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D23" s="40" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E23" s="17"/>
       <c r="F23" s="41" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G23" s="41" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H23" s="41" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="I23" s="40" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="J23" s="40" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="K23" s="40" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="24" ht="43" customHeight="1" spans="1:11">
       <c r="A24" s="42" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B24" s="43"/>
       <c r="C24" s="42" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D24" s="44" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E24" s="45"/>
       <c r="F24" s="46">
@@ -3658,25 +3661,25 @@
         <v>30</v>
       </c>
       <c r="I24" s="42" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J24" s="42" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="K24" s="48" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="25" ht="43" customHeight="1" spans="1:11">
       <c r="A25" s="42" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B25" s="43"/>
       <c r="C25" s="42" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D25" s="44" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E25" s="45"/>
       <c r="F25" s="46">
@@ -3689,23 +3692,23 @@
         <v>5</v>
       </c>
       <c r="I25" s="42" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J25" s="42"/>
       <c r="K25" s="49"/>
     </row>
     <row r="26" ht="43" customHeight="1" spans="1:11">
       <c r="A26" s="42" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B26" s="43" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C26" s="42" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D26" s="44" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E26" s="45"/>
       <c r="F26" s="46">
@@ -3718,27 +3721,27 @@
         <v>30</v>
       </c>
       <c r="I26" s="42" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J26" s="42" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="K26" s="49" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="27" ht="43" customHeight="1" spans="1:11">
       <c r="A27" s="42" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B27" s="43" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C27" s="42" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D27" s="44" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E27" s="45"/>
       <c r="F27" s="46">
@@ -3751,23 +3754,23 @@
         <v>50</v>
       </c>
       <c r="I27" s="42" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J27" s="42" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="K27" s="49"/>
     </row>
     <row r="28" ht="43" customHeight="1" spans="1:11">
       <c r="A28" s="42" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B28" s="43"/>
       <c r="C28" s="42" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D28" s="44" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E28" s="45"/>
       <c r="F28" s="46"/>
@@ -3776,19 +3779,19 @@
       <c r="I28" s="42"/>
       <c r="J28" s="42"/>
       <c r="K28" s="48" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="29" ht="43" customHeight="1" spans="1:11">
       <c r="A29" s="42" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B29" s="43"/>
       <c r="C29" s="42" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D29" s="44" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E29" s="45"/>
       <c r="F29" s="46"/>
@@ -3797,19 +3800,19 @@
       <c r="I29" s="42"/>
       <c r="J29" s="42"/>
       <c r="K29" s="48" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="30" ht="22" customHeight="1" spans="1:11">
       <c r="A30" s="50" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B30" s="51"/>
       <c r="C30" s="51" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D30" s="52" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E30" s="45"/>
       <c r="F30" s="46">
@@ -3822,23 +3825,23 @@
         <v>5</v>
       </c>
       <c r="I30" s="42" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J30" s="42" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="K30" s="53"/>
     </row>
     <row r="31" ht="22" customHeight="1" spans="1:11">
       <c r="A31" s="54" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B31" s="55"/>
       <c r="C31" s="55" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D31" s="56" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E31" s="45"/>
       <c r="F31" s="46">
@@ -3851,10 +3854,10 @@
         <v>5</v>
       </c>
       <c r="I31" s="55" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J31" s="42" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="K31" s="57"/>
     </row>
@@ -3938,7 +3941,7 @@
     </row>
     <row r="39" ht="39" customHeight="1" spans="1:11">
       <c r="A39" s="11" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B39" s="12"/>
       <c r="C39" s="12"/>
@@ -3953,7 +3956,7 @@
     </row>
     <row r="40" ht="30" customHeight="1" spans="1:11">
       <c r="A40" s="63" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B40" s="64"/>
       <c r="C40" s="64"/>
@@ -3968,32 +3971,32 @@
     </row>
     <row r="41" ht="37" customHeight="1" spans="1:11">
       <c r="A41" s="66" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B41" s="40" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C41" s="17"/>
       <c r="D41" s="40" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E41" s="41" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F41" s="41" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G41" s="40" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H41" s="40" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="I41" s="40" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="J41" s="40" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="K41" s="17"/>
     </row>
@@ -4002,11 +4005,11 @@
         <v>1</v>
       </c>
       <c r="B42" s="67" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C42" s="17"/>
       <c r="D42" s="42" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E42" s="46">
         <v>46122</v>
@@ -4021,10 +4024,10 @@
         <v>100</v>
       </c>
       <c r="I42" s="42" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="J42" s="69" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="K42" s="17"/>
     </row>
@@ -4033,11 +4036,11 @@
         <v>2</v>
       </c>
       <c r="B43" s="67" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C43" s="17"/>
       <c r="D43" s="42" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E43" s="46">
         <v>46134</v>
@@ -4052,10 +4055,10 @@
         <v>100</v>
       </c>
       <c r="I43" s="42" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="J43" s="69" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="K43" s="17"/>
     </row>
@@ -4064,11 +4067,11 @@
         <v>2</v>
       </c>
       <c r="B44" s="67" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C44" s="17"/>
       <c r="D44" s="42" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E44" s="46">
         <v>46134</v>
@@ -4083,10 +4086,10 @@
         <v>100</v>
       </c>
       <c r="I44" s="42" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="J44" s="69" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="K44" s="17"/>
     </row>
@@ -4095,11 +4098,11 @@
         <v>3</v>
       </c>
       <c r="B45" s="67" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C45" s="17"/>
       <c r="D45" s="42" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E45" s="46">
         <v>46138</v>
@@ -4114,7 +4117,7 @@
         <v>100</v>
       </c>
       <c r="I45" s="42" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="J45" s="69"/>
       <c r="K45" s="17"/>
@@ -4124,11 +4127,11 @@
         <v>4</v>
       </c>
       <c r="B46" s="67" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C46" s="17"/>
       <c r="D46" s="42" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E46" s="46">
         <v>46148</v>
@@ -4143,7 +4146,7 @@
         <v>100</v>
       </c>
       <c r="I46" s="42" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="J46" s="69"/>
       <c r="K46" s="17"/>
@@ -4153,11 +4156,11 @@
         <v>5</v>
       </c>
       <c r="B47" s="67" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C47" s="17"/>
       <c r="D47" s="42" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E47" s="46">
         <v>46152</v>
@@ -4172,7 +4175,7 @@
         <v>100</v>
       </c>
       <c r="I47" s="42" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="J47" s="69"/>
       <c r="K47" s="17"/>
@@ -4182,11 +4185,11 @@
         <v>6</v>
       </c>
       <c r="B48" s="67" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C48" s="17"/>
       <c r="D48" s="42" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E48" s="46">
         <v>46158</v>
@@ -4201,7 +4204,7 @@
         <v>100</v>
       </c>
       <c r="I48" s="42" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="J48" s="69"/>
       <c r="K48" s="17"/>
@@ -4211,11 +4214,11 @@
         <v>7</v>
       </c>
       <c r="B49" s="67" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C49" s="17"/>
       <c r="D49" s="42" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E49" s="46">
         <v>46166</v>
@@ -4230,10 +4233,10 @@
         <v>100</v>
       </c>
       <c r="I49" s="42" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="J49" s="69" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="K49" s="17"/>
     </row>
@@ -4242,11 +4245,11 @@
         <v>8</v>
       </c>
       <c r="B50" s="67" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C50" s="17"/>
       <c r="D50" s="42" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E50" s="46">
         <v>46140</v>
@@ -4261,21 +4264,21 @@
         <v>100</v>
       </c>
       <c r="I50" s="42" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="J50" s="69"/>
       <c r="K50" s="17"/>
     </row>
-    <row r="51" ht="30" spans="1:11">
+    <row r="51" ht="36" spans="1:11">
       <c r="A51" s="43">
         <v>8</v>
       </c>
       <c r="B51" s="67" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C51" s="17"/>
       <c r="D51" s="70" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E51" s="46">
         <v>46169</v>
@@ -4290,7 +4293,7 @@
         <v>60</v>
       </c>
       <c r="I51" s="42" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J51" s="69"/>
       <c r="K51" s="17"/>
@@ -4300,11 +4303,11 @@
         <v>9</v>
       </c>
       <c r="B52" s="67" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C52" s="17"/>
       <c r="D52" s="70" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E52" s="46">
         <v>46170</v>
@@ -4319,7 +4322,7 @@
         <v>100</v>
       </c>
       <c r="I52" s="42" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="J52" s="69"/>
       <c r="K52" s="17"/>
@@ -4329,11 +4332,11 @@
         <v>10</v>
       </c>
       <c r="B53" s="67" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C53" s="17"/>
       <c r="D53" s="70" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E53" s="46">
         <v>46173</v>
@@ -4348,7 +4351,7 @@
         <v>100</v>
       </c>
       <c r="I53" s="42" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="J53" s="69"/>
       <c r="K53" s="17"/>
@@ -4358,11 +4361,11 @@
         <v>11</v>
       </c>
       <c r="B54" s="67" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C54" s="17"/>
       <c r="D54" s="70" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E54" s="46">
         <v>46176</v>
@@ -4377,7 +4380,7 @@
         <v>100</v>
       </c>
       <c r="I54" s="42" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="J54" s="69"/>
       <c r="K54" s="17"/>
@@ -4387,11 +4390,11 @@
         <v>12</v>
       </c>
       <c r="B55" s="67" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C55" s="17"/>
       <c r="D55" s="70" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E55" s="46">
         <v>46182</v>
@@ -4402,7 +4405,7 @@
       <c r="G55" s="46"/>
       <c r="H55" s="47"/>
       <c r="I55" s="42" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="J55" s="69"/>
       <c r="K55" s="17"/>
@@ -4412,11 +4415,11 @@
         <v>13</v>
       </c>
       <c r="B56" s="67" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C56" s="17"/>
       <c r="D56" s="70" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E56" s="46">
         <v>46185</v>
@@ -4427,7 +4430,7 @@
       <c r="G56" s="46"/>
       <c r="H56" s="47"/>
       <c r="I56" s="42" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="J56" s="69"/>
       <c r="K56" s="17"/>
@@ -4437,11 +4440,11 @@
         <v>14</v>
       </c>
       <c r="B57" s="67" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C57" s="17"/>
       <c r="D57" s="70" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E57" s="46">
         <v>46189</v>
@@ -4452,7 +4455,7 @@
       <c r="G57" s="46"/>
       <c r="H57" s="47"/>
       <c r="I57" s="42" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="J57" s="69"/>
       <c r="K57" s="17"/>
@@ -4462,11 +4465,11 @@
         <v>34</v>
       </c>
       <c r="B58" s="67" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C58" s="17"/>
       <c r="D58" s="70" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E58" s="46">
         <v>46189</v>
@@ -4479,10 +4482,10 @@
         <v>0</v>
       </c>
       <c r="I58" s="42" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="J58" s="69" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="K58" s="17"/>
     </row>
@@ -4548,7 +4551,7 @@
     </row>
     <row r="64" ht="34" customHeight="1" spans="1:11">
       <c r="A64" s="80" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B64" s="81"/>
       <c r="C64" s="81"/>
@@ -4690,14 +4693,14 @@
     <tabColor rgb="FF7030A0"/>
   </sheetPr>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
-    <col min="1" max="1" width="66.9" customWidth="1"/>
+    <col min="1" max="1" width="66.9038461538462" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
   </sheetData>
